--- a/quizzes/sculpture-20e.xlsx
+++ b/quizzes/sculpture-20e.xlsx
@@ -856,7 +856,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>c.1905</t>
+          <t>environ 1905</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>c.1902</t>
+          <t>environ 1902</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">

--- a/quizzes/sculpture-20e.xlsx
+++ b/quizzes/sculpture-20e.xlsx
@@ -526,62 +526,62 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/e0/Adolfo_wildt%2C_vir_temporis_acti_%28uomo_antico%29%2C_1914-19_ca._%28mi%2C_gam%29.jpg/1280px-Adolfo_wildt%2C_vir_temporis_acti_%28uomo_antico%29%2C_1914-19_ca._%28mi%2C_gam%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/b/b1/BEETHovenAROlson.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Adolfo</t>
+          <t>Naum</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>WILDT</t>
+          <t>ARONSON</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1931</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>environ 1902</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Bonn</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Galleria d'Arte Moderna</t>
+          <t>Musée Beethoven</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>"Vir Temporis Acti (Uomo antico)"</t>
+          <t>"Buste de Beethoven"</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>c.100 cm</t>
+          <t>c.60 cm</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>italienne</t>
+          <t>russe</t>
         </is>
       </c>
       <c r="U2" t="n">
@@ -591,17 +591,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/ff/Swann_Memorial_Fountain%2C_Philadelphia.jpg/1280px-Swann_Memorial_Fountain%2C_Philadelphia.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f7/Schwebender_Engel.jpg/1280px-Schwebender_Engel.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Alexander Stirling</t>
+          <t>Ernst</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CALDER</t>
+          <t>BARLACH</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -611,37 +611,37 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>1938</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1924</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Philadelphie</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Logan Circle</t>
+          <t>Cathédrale de Güstrow</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>"Fontaine Swann"</t>
+          <t>"Der Schwebende (L'Ange planant)"</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bronze et granit</t>
+          <t>Bronze</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>c.200 cm</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>américaine</t>
+          <t>allemande</t>
         </is>
       </c>
       <c r="U3" t="n">
@@ -651,57 +651,57 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/51/Queen_Alexandra_Memorial%2C_Marlborough_Road.jpg/1280px-Queen_Alexandra_Memorial%2C_Marlborough_Road.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/bb/Fuente_de_los_Ni%C3%B1os_%281928%29.jpg/1280px-Fuente_de_los_Ni%C3%B1os_%281928%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Alfred</t>
+          <t>Mariano</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GILBERT</t>
+          <t>BENLLIURE</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1854</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1926-1932</t>
+          <t>1928</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Londres</t>
+          <t>Cantabrie</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Marlborough Road</t>
+          <t>Finca du marquis de Valdecilla</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>"Queen Alexandra Memorial"</t>
+          <t>"Fuente de los Niños"</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Bronze et pierre</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>anglaise (Royaume-Uni)</t>
+          <t>espagnole</t>
         </is>
       </c>
       <c r="U4" t="n">
@@ -711,52 +711,62 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/45/Triton_Babies%2C_Public_Garden%2C_Boston%2C_MA_-_IMG_5470.JPG/1280px-Triton_Babies%2C_Public_Garden%2C_Boston%2C_MA_-_IMG_5470.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/36/Joseph-Antoine_Bernard%2C_La_porteuse_d%27eau_Jeune_fille_%C3%A0_la_cruche%2C_%2C_KMSr115%2C_Statens_Museum_for_Kunst.jpg/1280px-Joseph-Antoine_Bernard%2C_La_porteuse_d%27eau_Jeune_fille_%C3%A0_la_cruche%2C_%2C_KMSr115%2C_Statens_Museum_for_Kunst.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Anna Coleman</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LADD</t>
+          <t>BERNARD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1878</t>
+          <t>1866</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>1931</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>1910</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Copenhague</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Boston Public Garden</t>
+          <t>Statens Museum for Kunst</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>"Triton Babies"</t>
+          <t>"La Porteuse d'eau (Jeune fille à la cruche)"</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Marbre</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>c.165 cm</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>américaine</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U5" t="n">
@@ -766,62 +776,57 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/65/Herakles-Archer_by_Antoine_Bourdelle%2C_c._1909%2C_bronze_-_Chazen_Museum_of_Art_-_DSC02262.JPG/1280px-Herakles-Archer_by_Antoine_Bourdelle%2C_c._1909%2C_bronze_-_Chazen_Museum_of_Art_-_DSC02262.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/91/Louisiana_Purchase_Monument_designed_by_Karl_Bitter_seen_from_the_south_on_the_Plaza_of_St._Louis_at_the_1904_World%27s_Fair.jpg/1280px-Louisiana_Purchase_Monument_designed_by_Karl_Bitter_seen_from_the_south_on_the_Plaza_of_St._Louis_at_the_1904_World%27s_Fair.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Antoine</t>
+          <t>Karl</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BOURDELLE</t>
+          <t>BITTER</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>1867</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>1904</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Saint-Louis</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Musée Bourdelle</t>
+          <t>Forest Park</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>"Héraklès archer"</t>
+          <t>"Louisiana Purchase Monument"</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bronze</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>c.250 cm</t>
+          <t>Pierre</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>autrichienne</t>
         </is>
       </c>
       <c r="U6" t="n">
@@ -831,62 +836,57 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/92/La_M%C3%A9diterran%C3%A9e_Statue_Maillol_Mus%C3%A9e_d%27Orsay.JPG/1280px-La_M%C3%A9diterran%C3%A9e_Statue_Maillol_Mus%C3%A9e_d%27Orsay.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/87/Mount_Rushmore_detail_view_%28100MP%29.jpg/1280px-Mount_Rushmore_detail_view_%28100MP%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Aristide</t>
+          <t>Gutzon</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MAILLOL</t>
+          <t>BORGLUM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>1867</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>environ 1905</t>
+          <t>1927-1941</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Dakota du Sud</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Musée d'Orsay</t>
+          <t>Mount Rushmore</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>"La Méditerranée"</t>
+          <t>"Mount Rushmore (visages des présidents)"</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Pierre</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>c.110 cm</t>
+          <t>Granit</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>américaine</t>
         </is>
       </c>
       <c r="U7" t="n">
@@ -896,32 +896,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/66/L72_-_Mus%C3%A9e_Rodin_-_L%27Homme_qui_marche.JPG/1280px-L72_-_Mus%C3%A9e_Rodin_-_L%27Homme_qui_marche.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/65/Herakles-Archer_by_Antoine_Bourdelle%2C_c._1909%2C_bronze_-_Chazen_Museum_of_Art_-_DSC02262.JPG/1280px-Herakles-Archer_by_Antoine_Bourdelle%2C_c._1909%2C_bronze_-_Chazen_Museum_of_Art_-_DSC02262.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Auguste</t>
+          <t>Antoine</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RODIN</t>
+          <t>BOURDELLE</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1840</t>
+          <t>1861</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>1929</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Musée Rodin</t>
+          <t>Musée Bourdelle</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>"L'Homme qui marche"</t>
+          <t>"Héraklès archer"</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>213,5 cm</t>
+          <t>c.250 cm</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -961,57 +961,57 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1b/Angel%2C_horse_%26_Sherman_at_Grand_Army_Plaza_in_Manhattan_07.jpg/1280px-Angel%2C_horse_%26_Sherman_at_Grand_Army_Plaza_in_Manhattan_07.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/61/Deux_lamas_-_Rembrandt_Bugatti_%28RF_3060%29_01.jpg/1280px-Deux_lamas_-_Rembrandt_Bugatti_%28RF_3060%29_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Augustus</t>
+          <t>Rembrandt</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SAINT-GAUDENS</t>
+          <t>BUGATTI</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>1884</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1892-1903</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Grand Army Plaza</t>
+          <t>Musée d'Orsay</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>"Monument au général Sherman"</t>
+          <t>"Deux lamas"</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bronze doré</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>américaine</t>
+          <t>italienne</t>
         </is>
       </c>
       <c r="U9" t="n">
@@ -1021,52 +1021,52 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/2c/Artemis_by_Bela_Lyon_Pratt%2C_1908%2C_bronze_-_New_Britain_Museum_of_American_Art_-_DSC09437.JPG/1280px-Artemis_by_Bela_Lyon_Pratt%2C_1908%2C_bronze_-_New_Britain_Museum_of_American_Art_-_DSC09437.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/ff/Swann_Memorial_Fountain%2C_Philadelphia.jpg/1280px-Swann_Memorial_Fountain%2C_Philadelphia.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bela Lyon</t>
+          <t>Alexander Stirling</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PRATT</t>
+          <t>CALDER</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1908</t>
+          <t>1924</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Philadelphie</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>New Britain Museum of American Art</t>
+          <t>Logan Circle</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>"Artemis"</t>
+          <t>"Fontaine Swann"</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bronze</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>c.200 cm</t>
+          <t>Bronze et granit</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1146,47 +1146,47 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/51/Charles_Despiau%2C_Assia%2C_1937.jpg/1280px-Charles_Despiau%2C_Assia%2C_1937.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/56/The_Appeal_to_the_Great_Spirit%2C_Cyrus_E._Dallin%2C_Boston%2C_Mass._%28cropped%29.jpg/1280px-The_Appeal_to_the_Great_Spirit%2C_Cyrus_E._Dallin%2C_Boston%2C_Mass._%28cropped%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Charles</t>
+          <t>Cyrus</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DESPIAU</t>
+          <t>DALLIN</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1874</t>
+          <t>1861</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1946</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>1908-1909</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Anvers</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Middelheim Museum</t>
+          <t>Museum of Fine Arts</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>"Assia"</t>
+          <t>"Appeal to the Great Spirit"</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1194,14 +1194,9 @@
           <t>Bronze</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>c.170 cm</t>
-        </is>
-      </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>américaine</t>
         </is>
       </c>
       <c r="U12" t="n">
@@ -1211,47 +1206,47 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/56/The_Appeal_to_the_Great_Spirit%2C_Cyrus_E._Dallin%2C_Boston%2C_Mass._%28cropped%29.jpg/1280px-The_Appeal_to_the_Great_Spirit%2C_Cyrus_E._Dallin%2C_Boston%2C_Mass._%28cropped%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/51/Charles_Despiau%2C_Assia%2C_1937.jpg/1280px-Charles_Despiau%2C_Assia%2C_1937.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cyrus</t>
+          <t>Charles</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DALLIN</t>
+          <t>DESPIAU</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>1874</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1908-1909</t>
+          <t>1937</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Anvers</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Museum of Fine Arts</t>
+          <t>Middelheim Museum</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>"Appeal to the Great Spirit"</t>
+          <t>"Assia"</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1259,9 +1254,14 @@
           <t>Bronze</t>
         </is>
       </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>c.170 cm</t>
+        </is>
+      </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>américaine</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U13" t="n">
@@ -1331,32 +1331,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a9/Prospero_and_Ariel_%2894216050%29.jpg/1280px-Prospero_and_Ariel_%2894216050%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/51/Queen_Alexandra_Memorial%2C_Marlborough_Road.jpg/1280px-Queen_Alexandra_Memorial%2C_Marlborough_Road.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Eric</t>
+          <t>Alfred</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GILL</t>
+          <t>GILBERT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1932</t>
+          <t>1926-1932</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1366,17 +1366,17 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Broadcasting House</t>
+          <t>Marlborough Road</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>"Prospero and Ariel"</t>
+          <t>"Queen Alexandra Memorial"</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Pierre de Portland</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -1391,57 +1391,57 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f7/Schwebender_Engel.jpg/1280px-Schwebender_Engel.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a9/Prospero_and_Ariel_%2894216050%29.jpg/1280px-Prospero_and_Ariel_%2894216050%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ernst</t>
+          <t>Eric</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BARLACH</t>
+          <t>GILL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1938</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>1932</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Londres</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Cathédrale de Güstrow</t>
+          <t>Broadcasting House</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>"Der Schwebende (L'Ange planant)"</t>
+          <t>"Prospero and Ariel"</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bronze</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>c.200 cm</t>
+          <t>Pierre de Portland</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>allemande</t>
+          <t>anglaise (Royaume-Uni)</t>
         </is>
       </c>
       <c r="U16" t="n">
@@ -1451,62 +1451,62 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/6d/Pompon_LOursBlanc1.jpg/1280px-Pompon_LOursBlanc1.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/ba/Amsterdam_-_Stedelijk_Museum_-_Julio_Gonz%C3%A1lez_%281876-1942%29_-_La_Montserrat_%28BA_109%29_1935-37.jpg/1280px-Amsterdam_-_Stedelijk_Museum_-_Julio_Gonz%C3%A1lez_%281876-1942%29_-_La_Montserrat_%28BA_109%29_1935-37.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>François</t>
+          <t>Julio</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>POMPON</t>
+          <t>GONZÁLEZ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>1876</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>1942</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1927-1929</t>
+          <t>1935-1937</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Amsterdam</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Musée d'Orsay</t>
+          <t>Stedelijk Museum</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>"Ours blanc"</t>
+          <t>"La Montserrat"</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Pierre</t>
+          <t>Fer forgé</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>c.163 cm</t>
+          <t>165 cm</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>espagnole</t>
         </is>
       </c>
       <c r="U17" t="n">
@@ -1516,62 +1516,57 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a9/Georg_Kolbe_Der_Morgen.jpg/1280px-Georg_Kolbe_Der_Morgen.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/06/Mirabeau_par_Injabert_2.JPG/1280px-Mirabeau_par_Injabert_2.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Georg</t>
+          <t>Jean-Antoine</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>KOLBE</t>
+          <t>INJALBERT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1877</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>1905-1906</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Ceciliengärten</t>
+          <t>Panthéon</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>"Der Morgen (Le Matin)"</t>
+          <t>"Statue de Mirabeau"</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bronze</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>c.195 cm</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>allemande</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U18" t="n">
@@ -1581,57 +1576,62 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/87/Mount_Rushmore_detail_view_%28100MP%29.jpg/1280px-Mount_Rushmore_detail_view_%28100MP%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a9/Georg_Kolbe_Der_Morgen.jpg/1280px-Georg_Kolbe_Der_Morgen.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Gutzon</t>
+          <t>Georg</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BORGLUM</t>
+          <t>KOLBE</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>1877</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1927-1941</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Dakota du Sud</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Mount Rushmore</t>
+          <t>Ceciliengärten</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>"Mount Rushmore (visages des présidents)"</t>
+          <t>"Der Morgen (Le Matin)"</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Granit</t>
+          <t>Bronze</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>c.195 cm</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>américaine</t>
+          <t>allemande</t>
         </is>
       </c>
       <c r="U19" t="n">
@@ -1641,57 +1641,62 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/06/Mirabeau_par_Injabert_2.JPG/1280px-Mirabeau_par_Injabert_2.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/56/Museum_am_Dom_7.jpg/1280px-Museum_am_Dom_7.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Jean-Antoine</t>
+          <t>Käthe</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>INJALBERT</t>
+          <t>KOLLWITZ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>1867</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1905-1906</t>
+          <t>1937-1938</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Cologne</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Panthéon</t>
+          <t>Käthe-Kollwitz-Museum</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>"Statue de Mirabeau"</t>
+          <t>"Mère avec son fils mort (Pietà)"</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Bronze</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>c.38 cm</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>allemande</t>
         </is>
       </c>
       <c r="U20" t="n">
@@ -1701,62 +1706,52 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/36/Joseph-Antoine_Bernard%2C_La_porteuse_d%27eau_Jeune_fille_%C3%A0_la_cruche%2C_%2C_KMSr115%2C_Statens_Museum_for_Kunst.jpg/1280px-Joseph-Antoine_Bernard%2C_La_porteuse_d%27eau_Jeune_fille_%C3%A0_la_cruche%2C_%2C_KMSr115%2C_Statens_Museum_for_Kunst.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/45/Triton_Babies%2C_Public_Garden%2C_Boston%2C_MA_-_IMG_5470.JPG/1280px-Triton_Babies%2C_Public_Garden%2C_Boston%2C_MA_-_IMG_5470.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>Anna Coleman</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BERNARD</t>
+          <t>LADD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1866</t>
+          <t>1878</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1931</t>
+          <t>1939</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1910</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Copenhague</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Statens Museum for Kunst</t>
+          <t>Boston Public Garden</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>"La Porteuse d'eau (Jeune fille à la cruche)"</t>
+          <t>"Triton Babies"</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Marbre</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>c.165 cm</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>américaine</t>
         </is>
       </c>
       <c r="U21" t="n">
@@ -1766,62 +1761,67 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/ba/Amsterdam_-_Stedelijk_Museum_-_Julio_Gonz%C3%A1lez_%281876-1942%29_-_La_Montserrat_%28BA_109%29_1935-37.jpg/1280px-Amsterdam_-_Stedelijk_Museum_-_Julio_Gonz%C3%A1lez_%281876-1942%29_-_La_Montserrat_%28BA_109%29_1935-37.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/e6/Lehmbruck_-_die_Gest%C3%BCrzte.jpg/1280px-Lehmbruck_-_die_Gest%C3%BCrzte.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Julio</t>
+          <t>Wilhelm</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GONZÁLEZ</t>
+          <t>LEHMBRUCK</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1876</t>
+          <t>1881</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1942</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1935-1937</t>
+          <t>1915-1916</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Amsterdam</t>
+          <t>Duisbourg</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Stedelijk Museum</t>
+          <t>Lehmbruck Museum</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>"La Montserrat"</t>
+          <t>"Der Gestürzte (L'Homme foudroyé)"</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Fer forgé</t>
+          <t>Pierre reconstituée</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>165 cm</t>
+          <t>78 cm</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>240 cm</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>espagnole</t>
+          <t>allemande</t>
         </is>
       </c>
       <c r="U22" t="n">
@@ -1831,47 +1831,47 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/91/Louisiana_Purchase_Monument_designed_by_Karl_Bitter_seen_from_the_south_on_the_Plaza_of_St._Louis_at_the_1904_World%27s_Fair.jpg/1280px-Louisiana_Purchase_Monument_designed_by_Karl_Bitter_seen_from_the_south_on_the_Plaza_of_St._Louis_at_the_1904_World%27s_Fair.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/92/La_M%C3%A9diterran%C3%A9e_Statue_Maillol_Mus%C3%A9e_d%27Orsay.JPG/1280px-La_M%C3%A9diterran%C3%A9e_Statue_Maillol_Mus%C3%A9e_d%27Orsay.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Karl</t>
+          <t>Aristide</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BITTER</t>
+          <t>MAILLOL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>1861</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1904</t>
+          <t>environ 1905</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Saint-Louis</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Forest Park</t>
+          <t>Musée d'Orsay</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>"Louisiana Purchase Monument"</t>
+          <t>"La Méditerranée"</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -1879,9 +1879,14 @@
           <t>Pierre</t>
         </is>
       </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>c.110 cm</t>
+        </is>
+      </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>autrichienne</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U23" t="n">
@@ -1891,62 +1896,62 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/56/Museum_am_Dom_7.jpg/1280px-Museum_am_Dom_7.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/5f/%D0%A0%D0%B0%D0%B1%D0%BE%D1%87%D0%B8%D0%B9_%D0%B8_%D0%BA%D0%BE%D0%BB%D1%85%D0%BE%D0%B7%D0%BD%D0%B8%D1%86%D0%B0_%D0%9F%D0%B0%D0%B2%D0%B8%D0%BB%D1%8C%D0%BE%D0%BD_%D0%A1%D0%A1%D0%A1%D0%A0_%D0%9F%D0%B0%D1%80%D0%B8%D0%B6_1937_%28%D0%9A%D0%BE%D0%BB%D0%BE%D1%80%D0%B8%D0%B7%D0%BE%D0%B2%D0%B0%D0%BD%D0%BD%D0%B0%D1%8F%29_%28cropped%29.png/960px-%D0%A0%D0%B0%D0%B1%D0%BE%D1%87%D0%B8%D0%B9_%D0%B8_%D0%BA%D0%BE%D0%BB%D1%85%D0%BE%D0%B7%D0%BD%D0%B8%D1%86%D0%B0_%D0%9F%D0%B0%D0%B2%D0%B8%D0%BB%D1%8C%D0%BE%D0%BD_%D0%A1%D0%A1%D0%A1%D0%A0_%D0%9F%D0%B0%D1%80%D0%B8%D0%B6_1937_%28%D0%9A%D0%BE%D0%BB%D0%BE%D1%80%D0%B8%D0%B7%D0%BE%D0%B2%D0%B0%D0%BD%D0%BD%D0%B0%D1%8F%29_%28cropped%29.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Käthe</t>
+          <t>Vera</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>KOLLWITZ</t>
+          <t>MUKHINA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>1889</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>1953</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1937-1938</t>
+          <t>1937</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Cologne</t>
+          <t>Moscou</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Käthe-Kollwitz-Museum</t>
+          <t>VDNKh</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>"Mère avec son fils mort (Pietà)"</t>
+          <t>"L'Ouvrier et la Kolkhozienne"</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Acier inoxydable</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>c.38 cm</t>
+          <t>24,5 m</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>allemande</t>
+          <t>russe</t>
         </is>
       </c>
       <c r="U24" t="n">
@@ -1956,57 +1961,62 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a3/Panorama_of_the_Fountain_of_Time.JPG/1280px-Panorama_of_the_Fountain_of_Time.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/6d/Pompon_LOursBlanc1.jpg/1280px-Pompon_LOursBlanc1.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lorado</t>
+          <t>François</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TAFT</t>
+          <t>POMPON</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1920-1922</t>
+          <t>1927-1929</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Washington Park</t>
+          <t>Musée d'Orsay</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>"Fountain of Time"</t>
+          <t>"Ours blanc"</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Béton</t>
+          <t>Pierre</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>c.163 cm</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>américaine</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U25" t="n">
@@ -2016,57 +2026,57 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/bb/Fuente_de_los_Ni%C3%B1os_%281928%29.jpg/1280px-Fuente_de_los_Ni%C3%B1os_%281928%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/2c/Artemis_by_Bela_Lyon_Pratt%2C_1908%2C_bronze_-_New_Britain_Museum_of_American_Art_-_DSC09437.JPG/1280px-Artemis_by_Bela_Lyon_Pratt%2C_1908%2C_bronze_-_New_Britain_Museum_of_American_Art_-_DSC09437.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mariano</t>
+          <t>Bela Lyon</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BENLLIURE</t>
+          <t>PRATT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>1867</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1928</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Cantabrie</t>
+          <t>1908</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Finca du marquis de Valdecilla</t>
+          <t>New Britain Museum of American Art</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>"Fuente de los Niños"</t>
+          <t>"Artemis"</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bronze et pierre</t>
+          <t>Bronze</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>c.200 cm</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>espagnole</t>
+          <t>américaine</t>
         </is>
       </c>
       <c r="U26" t="n">
@@ -2076,47 +2086,47 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/b/b1/BEETHovenAROlson.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/66/L72_-_Mus%C3%A9e_Rodin_-_L%27Homme_qui_marche.JPG/1280px-L72_-_Mus%C3%A9e_Rodin_-_L%27Homme_qui_marche.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Naum</t>
+          <t>Auguste</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ARONSON</t>
+          <t>RODIN</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>environ 1902</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Bonn</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Musée Beethoven</t>
+          <t>Musée Rodin</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>"Buste de Beethoven"</t>
+          <t>"L'Homme qui marche"</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2126,12 +2136,12 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>c.60 cm</t>
+          <t>213,5 cm</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>russe</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U27" t="n">
@@ -2141,57 +2151,57 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/8e/Trubetzkoy_Children.jpg/960px-Trubetzkoy_Children.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1b/Angel%2C_horse_%26_Sherman_at_Grand_Army_Plaza_in_Manhattan_07.jpg/1280px-Angel%2C_horse_%26_Sherman_at_Grand_Army_Plaza_in_Manhattan_07.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Augustus</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>TROUBETZKOY</t>
+          <t>SAINT-GAUDENS</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1866</t>
+          <t>1848</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1938</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1892-1903</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Saint Petersbourg</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Musée russe</t>
+          <t>Grand Army Plaza</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>"Enfants"</t>
+          <t>"Monument au général Sherman"</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Bronze doré</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>russe</t>
+          <t>américaine</t>
         </is>
       </c>
       <c r="U28" t="n">
@@ -2201,57 +2211,57 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/61/Deux_lamas_-_Rembrandt_Bugatti_%28RF_3060%29_01.jpg/1280px-Deux_lamas_-_Rembrandt_Bugatti_%28RF_3060%29_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a3/Panorama_of_the_Fountain_of_Time.JPG/1280px-Panorama_of_the_Fountain_of_Time.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Rembrandt</t>
+          <t>Lorado</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BUGATTI</t>
+          <t>TAFT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1884</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1916</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1911</t>
+          <t>1920-1922</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Musée d'Orsay</t>
+          <t>Washington Park</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>"Deux lamas"</t>
+          <t>"Fountain of Time"</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Béton</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>italienne</t>
+          <t>américaine</t>
         </is>
       </c>
       <c r="U29" t="n">
@@ -2261,57 +2271,52 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/5f/%D0%A0%D0%B0%D0%B1%D0%BE%D1%87%D0%B8%D0%B9_%D0%B8_%D0%BA%D0%BE%D0%BB%D1%85%D0%BE%D0%B7%D0%BD%D0%B8%D1%86%D0%B0_%D0%9F%D0%B0%D0%B2%D0%B8%D0%BB%D1%8C%D0%BE%D0%BD_%D0%A1%D0%A1%D0%A1%D0%A0_%D0%9F%D0%B0%D1%80%D0%B8%D0%B6_1937_%28%D0%9A%D0%BE%D0%BB%D0%BE%D1%80%D0%B8%D0%B7%D0%BE%D0%B2%D0%B0%D0%BD%D0%BD%D0%B0%D1%8F%29_%28cropped%29.png/960px-%D0%A0%D0%B0%D0%B1%D0%BE%D1%87%D0%B8%D0%B9_%D0%B8_%D0%BA%D0%BE%D0%BB%D1%85%D0%BE%D0%B7%D0%BD%D0%B8%D1%86%D0%B0_%D0%9F%D0%B0%D0%B2%D0%B8%D0%BB%D1%8C%D0%BE%D0%BD_%D0%A1%D0%A1%D0%A1%D0%A0_%D0%9F%D0%B0%D1%80%D0%B8%D0%B6_1937_%28%D0%9A%D0%BE%D0%BB%D0%BE%D1%80%D0%B8%D0%B7%D0%BE%D0%B2%D0%B0%D0%BD%D0%BD%D0%B0%D1%8F%29_%28cropped%29.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/8e/Trubetzkoy_Children.jpg/960px-Trubetzkoy_Children.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Vera</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MUKHINA</t>
+          <t>TROUBETZKOY</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1889</t>
+          <t>1866</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>1938</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Moscou</t>
+          <t>Saint Petersbourg</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>VDNKh</t>
+          <t>Musée russe</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>"L'Ouvrier et la Kolkhozienne"</t>
+          <t>"Enfants"</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Acier inoxydable</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>24,5 m</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
@@ -2326,67 +2331,62 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/e6/Lehmbruck_-_die_Gest%C3%BCrzte.jpg/1280px-Lehmbruck_-_die_Gest%C3%BCrzte.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/e0/Adolfo_wildt%2C_vir_temporis_acti_%28uomo_antico%29%2C_1914-19_ca._%28mi%2C_gam%29.jpg/1280px-Adolfo_wildt%2C_vir_temporis_acti_%28uomo_antico%29%2C_1914-19_ca._%28mi%2C_gam%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Wilhelm</t>
+          <t>Adolfo</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>LEHMBRUCK</t>
+          <t>WILDT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1881</t>
+          <t>1868</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>1931</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1915-1916</t>
+          <t>1921</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Duisbourg</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Lehmbruck Museum</t>
+          <t>Galleria d'Arte Moderna</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>"Der Gestürzte (L'Homme foudroyé)"</t>
+          <t>"Vir Temporis Acti (Uomo antico)"</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Pierre reconstituée</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>78 cm</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>240 cm</t>
+          <t>c.100 cm</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>allemande</t>
+          <t>italienne</t>
         </is>
       </c>
       <c r="U31" t="n">

--- a/quizzes/sculpture-20e.xlsx
+++ b/quizzes/sculpture-20e.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>environ 1902</t>
+          <t>1902 environ</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>environ 1905</t>
+          <t>1905 environ</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
